--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:42:02+08:00</t>
+    <t>2026-07-10T19:56:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T19:56:53+08:00</t>
+    <t>2026-07-10T21:30:50+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T21:30:50+08:00</t>
+    <t>2026-07-23T22:22:27+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T22:22:27+08:00</t>
+    <t>2026-07-24T13:54:16+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2126" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2126" uniqueCount="435">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T13:54:16+08:00</t>
+    <t>2026-07-25T16:18:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -748,15 +748,6 @@
   </si>
   <si>
     <t>The title (eg "My Tasks", "Outstanding Tasks for Patient X") should go into the code.</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://snomed.info/sct"/&gt;
-    &lt;code value="315640000"/&gt;
-    &lt;display value="Occupational health counseling (procedure)"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Codes to identify what the task involves.  These will typically be specific to a particular workflow.</t>
@@ -4287,7 +4278,7 @@
         <v>22</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>237</v>
+        <v>22</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>22</v>
@@ -4305,10 +4296,10 @@
         <v>204</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="Z23" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>22</v>
@@ -4341,13 +4332,13 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>22</v>
@@ -4355,10 +4346,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4381,13 +4372,13 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4438,7 +4429,7 @@
         <v>22</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4456,7 +4447,7 @@
         <v>22</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>22</v>
@@ -4467,10 +4458,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4493,19 +4484,19 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>22</v>
@@ -4554,7 +4545,7 @@
         <v>22</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4572,10 +4563,10 @@
         <v>22</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>22</v>
@@ -4583,14 +4574,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4612,14 +4603,14 @@
         <v>171</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>22</v>
@@ -4668,7 +4659,7 @@
         <v>22</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4683,13 +4674,13 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>22</v>
@@ -4697,10 +4688,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4723,17 +4714,17 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>22</v>
@@ -4782,7 +4773,7 @@
         <v>22</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4797,13 +4788,13 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>22</v>
@@ -4811,10 +4802,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4837,13 +4828,13 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4894,7 +4885,7 @@
         <v>22</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4909,13 +4900,13 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>22</v>
@@ -4923,14 +4914,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4949,17 +4940,17 @@
         <v>22</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>22</v>
@@ -5008,7 +4999,7 @@
         <v>22</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5017,19 +5008,19 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AM29" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>22</v>
@@ -5037,14 +5028,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5063,17 +5054,17 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>22</v>
@@ -5122,7 +5113,7 @@
         <v>22</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5131,7 +5122,7 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>99</v>
@@ -5140,7 +5131,7 @@
         <v>22</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>22</v>
@@ -5151,10 +5142,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5177,17 +5168,17 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>22</v>
@@ -5236,7 +5227,7 @@
         <v>22</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5251,13 +5242,13 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>22</v>
@@ -5265,10 +5256,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5294,14 +5285,14 @@
         <v>200</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>22</v>
@@ -5329,11 +5320,11 @@
         <v>111</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="Z32" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="Z32" t="s" s="2">
-        <v>307</v>
-      </c>
       <c r="AA32" t="s" s="2">
         <v>22</v>
       </c>
@@ -5350,7 +5341,7 @@
         <v>22</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5365,13 +5356,13 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>22</v>
@@ -5379,14 +5370,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5405,19 +5396,19 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>22</v>
@@ -5466,7 +5457,7 @@
         <v>22</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5481,13 +5472,13 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AL33" t="s" s="2">
-        <v>319</v>
-      </c>
       <c r="AM33" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>22</v>
@@ -5495,10 +5486,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5521,17 +5512,17 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>22</v>
@@ -5580,7 +5571,7 @@
         <v>22</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5595,13 +5586,13 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>22</v>
@@ -5609,10 +5600,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5638,13 +5629,13 @@
         <v>200</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5673,7 +5664,7 @@
         <v>204</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>22</v>
@@ -5694,7 +5685,7 @@
         <v>22</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5709,24 +5700,24 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>336</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5752,13 +5743,13 @@
         <v>171</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M36" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5808,7 +5799,7 @@
         <v>22</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5823,13 +5814,13 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AL36" t="s" s="2">
-        <v>341</v>
-      </c>
       <c r="AM36" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>22</v>
@@ -5837,10 +5828,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5863,13 +5854,13 @@
         <v>22</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5920,7 +5911,7 @@
         <v>22</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5935,24 +5926,24 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>348</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5975,13 +5966,13 @@
         <v>22</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6032,7 +6023,7 @@
         <v>22</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6047,10 +6038,10 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>22</v>
@@ -6061,14 +6052,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6087,16 +6078,16 @@
         <v>22</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6146,7 +6137,7 @@
         <v>22</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6161,10 +6152,10 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>22</v>
@@ -6175,10 +6166,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6201,17 +6192,17 @@
         <v>22</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>22</v>
@@ -6260,7 +6251,7 @@
         <v>22</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6278,7 +6269,7 @@
         <v>22</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>22</v>
@@ -6289,10 +6280,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6315,13 +6306,13 @@
         <v>22</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6372,25 +6363,25 @@
         <v>22</v>
       </c>
       <c r="AF41" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>22</v>
@@ -6401,10 +6392,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6430,10 +6421,10 @@
         <v>132</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>149</v>
@@ -6486,7 +6477,7 @@
         <v>22</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6504,7 +6495,7 @@
         <v>22</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>22</v>
@@ -6515,14 +6506,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6544,10 +6535,10 @@
         <v>132</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>149</v>
@@ -6602,7 +6593,7 @@
         <v>22</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6631,10 +6622,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6657,17 +6648,17 @@
         <v>22</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>22</v>
@@ -6716,7 +6707,7 @@
         <v>22</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6734,7 +6725,7 @@
         <v>22</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>22</v>
@@ -6745,10 +6736,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6771,19 +6762,19 @@
         <v>22</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>22</v>
@@ -6832,7 +6823,7 @@
         <v>22</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6850,7 +6841,7 @@
         <v>22</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>22</v>
@@ -6861,10 +6852,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6887,13 +6878,13 @@
         <v>22</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6944,7 +6935,7 @@
         <v>22</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6962,7 +6953,7 @@
         <v>22</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>22</v>
@@ -6973,14 +6964,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6999,17 +6990,17 @@
         <v>22</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>22</v>
@@ -7058,7 +7049,7 @@
         <v>22</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7076,7 +7067,7 @@
         <v>22</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>22</v>
@@ -7087,10 +7078,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7113,13 +7104,13 @@
         <v>22</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7170,25 +7161,25 @@
         <v>22</v>
       </c>
       <c r="AF48" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>22</v>
@@ -7199,10 +7190,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7228,10 +7219,10 @@
         <v>132</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>149</v>
@@ -7284,7 +7275,7 @@
         <v>22</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7302,7 +7293,7 @@
         <v>22</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>22</v>
@@ -7313,14 +7304,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7342,10 +7333,10 @@
         <v>132</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>149</v>
@@ -7400,7 +7391,7 @@
         <v>22</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7429,14 +7420,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7458,16 +7449,16 @@
         <v>200</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>22</v>
@@ -7495,7 +7486,7 @@
         <v>204</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="Z51" t="s" s="2">
         <v>22</v>
@@ -7516,7 +7507,7 @@
         <v>22</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>87</v>
@@ -7534,7 +7525,7 @@
         <v>22</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>22</v>
@@ -7545,10 +7536,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7571,13 +7562,13 @@
         <v>22</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7628,7 +7619,7 @@
         <v>22</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>87</v>
@@ -7646,7 +7637,7 @@
         <v>22</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>22</v>
@@ -7657,10 +7648,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7683,17 +7674,17 @@
         <v>22</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>22</v>
@@ -7742,7 +7733,7 @@
         <v>22</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7760,7 +7751,7 @@
         <v>22</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>22</v>
@@ -7771,10 +7762,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7797,13 +7788,13 @@
         <v>22</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7854,25 +7845,25 @@
         <v>22</v>
       </c>
       <c r="AF54" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>22</v>
@@ -7883,10 +7874,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7912,10 +7903,10 @@
         <v>132</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>149</v>
@@ -7968,7 +7959,7 @@
         <v>22</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7986,7 +7977,7 @@
         <v>22</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>22</v>
@@ -7997,14 +7988,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8026,10 +8017,10 @@
         <v>132</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>149</v>
@@ -8084,7 +8075,7 @@
         <v>22</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8113,14 +8104,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8142,14 +8133,14 @@
         <v>200</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>22</v>
@@ -8177,7 +8168,7 @@
         <v>204</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Z57" t="s" s="2">
         <v>22</v>
@@ -8198,7 +8189,7 @@
         <v>22</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>87</v>
@@ -8216,7 +8207,7 @@
         <v>22</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>22</v>
@@ -8227,10 +8218,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8253,17 +8244,17 @@
         <v>22</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>22</v>
@@ -8312,7 +8303,7 @@
         <v>22</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>87</v>
@@ -8330,7 +8321,7 @@
         <v>22</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T16:18:15+08:00</t>
+    <t>2026-07-26T10:07:44+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T10:07:44+08:00</t>
+    <t>2026-07-26T12:18:37+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T12:18:37+08:00</t>
+    <t>2026-07-26T14:28:30+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>用於記錄臨場服務中針對發現問題所提出之改善建議措施，以及追蹤前次改善事項之落實情形（對應附表八）。</t>
+    <t>用於記錄臨場服務中針對發現問題所提出之改善建議措施，以及追蹤前次改善事項之落實情形（對應附表八）。
+**for／focus／owner 語意界定（回應委員意見）**：本資源表達「**後續改善工作**」。`focus` 指向所依據之現場發現（ServiceFinding）；`owner` 為負責執行改善之事業單位；若改善事項係針對特定勞工（如個別配工調整），以 `for` 表達該 Patient。**事業單位以 `owner` 表達，不置於 `for`。**</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T14:28:30+08:00</t>
+    <t>2026-07-26T15:21:49+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T15:21:49+08:00</t>
+    <t>2026-07-26T16:11:18+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T16:11:18+08:00</t>
+    <t>2026-07-26T18:45:10+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T18:45:10+08:00</t>
+    <t>2026-07-29T09:46:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>用於記錄臨場服務中針對發現問題所提出之改善建議措施，以及追蹤前次改善事項之落實情形（對應附表八）。
+    <t>用於記錄臨場服務中針對發現問題所提出之改善建議措施，以及追蹤前次改善事項之落實情形（對應附表八）。
 **for／focus／owner 語意界定（回應委員意見）**：本資源表達「**後續改善工作**」。`focus` 指向所依據之現場發現（ServiceFinding）；`owner` 為負責執行改善之事業單位；若改善事項係針對特定勞工（如個別配工調整），以 `for` 表達該 Patient。**事業單位以 `owner` 表達，不置於 `for`。**</t>
   </si>
   <si>
@@ -1682,15 +1682,15 @@
   <dimension ref="A1:AN58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="28.3984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="28.3984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.7578125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.80078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="27.80078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.30859375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1701,26 +1701,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="147.3828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="41.75" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="15.98046875" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="30.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="145.00390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="39.265625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="48.28515625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="94.5390625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="29.45703125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="22.43359375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="47.7734375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="94.296875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="24.1328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:46:30+00:00</t>
+    <t>2026-07-29T14:03:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T14:03:51+00:00</t>
+    <t>2026-07-29T16:26:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:26:07+00:00</t>
+    <t>2026-07-29T16:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:54:28+00:00</t>
+    <t>2026-07-30T07:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:25:13+00:00</t>
+    <t>2026-07-30T09:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:28:37+00:00</t>
+    <t>2026-07-30T10:44:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:44:37+00:00</t>
+    <t>2026-07-30T12:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:17:12+00:00</t>
+    <t>2026-07-30T14:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:17:56+00:00</t>
+    <t>2026-07-30T14:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:46:31+00:00</t>
+    <t>2026-08-05T16:28:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:28:11+00:00</t>
+    <t>2026-08-05T16:48:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:48:01+00:00</t>
+    <t>2026-08-17T03:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.3</t>
+    <t>0.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T03:02:16+00:00</t>
+    <t>2026-08-17T05:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.4</t>
+    <t>0.2.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T05:27:05+00:00</t>
+    <t>2026-08-17T06:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.5</t>
+    <t>0.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T06:57:01+00:00</t>
+    <t>2026-08-20T12:04:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T12:04:33+00:00</t>
+    <t>2026-08-20T13:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:40:11+00:00</t>
+    <t>2026-08-20T16:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>用於記錄臨場服務中針對發現問題所提出之改善建議措施，以及追蹤前次改善事項之落實情形（對應附表八）。
+    <t>【依據：勞工健康保護規則附表】用於記錄臨場服務中針對發現問題所提出之改善建議措施，以及追蹤前次改善事項之落實情形（對應附表八）。
 **for／focus／owner 語意界定（回應委員意見）**：本資源表達「**後續改善工作**」。`focus` 指向所依據之現場發現（ServiceFinding）；`owner` 為負責執行改善之事業單位；若改善事項係針對特定勞工（如個別配工調整），以 `for` 表達該 Patient。**事業單位以 `owner` 表達，不置於 `for`。**</t>
   </si>
   <si>
@@ -460,7 +460,7 @@
     <t>雇主事業單位資訊擴充</t>
   </si>
   <si>
-    <t>關聯受檢勞工所屬之事業單位組織資料，或臨場服務事件/活動所針對之事業單位。</t>
+    <t>【技術規格】關聯受檢勞工所屬之事業單位組織資料，或臨場服務事件/活動所針對之事業單位。</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:35:38+00:00</t>
+    <t>2026-08-20T17:39:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,6 +88,8 @@
   </si>
   <si>
     <t>【依據：勞工健康保護規則附表】用於記錄臨場服務中針對發現問題所提出之改善建議措施，以及追蹤前次改善事項之落實情形（對應附表八）。
+* ^status = #draft
+* ^extension[http://hl7.org/fhir/StructureDefinition/structuredefinition-standards-status].valueCode = #draft
 **for／focus／owner 語意界定（回應委員意見）**：本資源表達「**後續改善工作**」。`focus` 指向所依據之現場發現（ServiceFinding）；`owner` 為負責執行改善之事業單位；若改善事項係針對特定勞工（如個別配工調整），以 `for` 表達該 Patient。**事業單位以 `owner` 表達，不置於 `for`。**</t>
   </si>
   <si>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T17:39:23+00:00</t>
+    <t>2026-08-20T18:13:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,8 +88,6 @@
   </si>
   <si>
     <t>【依據：勞工健康保護規則附表】用於記錄臨場服務中針對發現問題所提出之改善建議措施，以及追蹤前次改善事項之落實情形（對應附表八）。
-* ^status = #draft
-* ^extension[http://hl7.org/fhir/StructureDefinition/structuredefinition-standards-status].valueCode = #draft
 **for／focus／owner 語意界定（回應委員意見）**：本資源表達「**後續改善工作**」。`focus` 指向所依據之現場發現（ServiceFinding）；`owner` 為負責執行改善之事業單位；若改善事項係針對特定勞工（如個別配工調整），以 `for` 表達該 Patient。**事業單位以 `owner` 表達，不置於 `for`。**</t>
   </si>
   <si>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.1</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T18:13:29+00:00</t>
+    <t>2026-08-21T00:14:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:14:56+00:00</t>
+    <t>2026-08-21T00:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.7.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:59:40+00:00</t>
+    <t>2026-08-21T01:22:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.1</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T01:22:55+00:00</t>
+    <t>2026-08-21T04:20:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.8.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T04:20:36+00:00</t>
+    <t>2026-08-21T12:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.5</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T12:32:47+00:00</t>
+    <t>2026-08-21T14:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:27:31+00:00</t>
+    <t>2026-08-21T15:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T15:06:05+00:00</t>
+    <t>2026-08-21T16:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.3</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:05:47+00:00</t>
+    <t>2026-08-22T02:14:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T02:14:01+00:00</t>
+    <t>2026-08-22T04:25:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.10.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T04:25:10+00:00</t>
+    <t>2026-08-22T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.1</t>
+    <t>0.10.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T08:31:54+00:00</t>
+    <t>2026-08-22T14:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Task-ServiceTask.xlsx
+++ b/StructureDefinition-TWHA-Task-ServiceTask.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.2</t>
+    <t>0.10.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T14:05:28+00:00</t>
+    <t>2026-08-22T17:09:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
